--- a/extenbooks/S1005_extenbook.xlsx
+++ b/extenbooks/S1005_extenbook.xlsx
@@ -15831,7 +15831,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>**Status**: ingested</t>
+          <t>**Status**: book_period_validated</t>
         </is>
       </c>
     </row>
@@ -16920,11 +16920,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -16947,88 +16947,6 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Dividend Yield vs Bond Yield</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>chapter</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>ingested</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>phases_completed</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>["3_research", "4_adequacy", "5_ingestion", "6_extension", "7_replication", "8_output"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>artifacts</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>{"research_json": "Technical/research/S1005_research.json", "adequacy_report": "Technical/docs/chapters/CH10_ADEQUACY_REPORT.json", "dpr": "Technical/docs/series/S1005_DPR.md", "epr": "Technical/docs/series/S1005_EPR.md", "loader": "Technical/code/L01_loaders/L01_S1005_load.py", "processor": "Technical/code/P02_processors/P02_S1005_construct.py", "validator": "Technical/code/V03_validators/V03_S1005_validate.py", "processed": "Technical/data/processed/S1005.parquet", "chopped_csv": "Technical/chopped/S1005.csv", "extenbook_xlsx": "Technical/extenbooks/S1005_extenbook.xlsx"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>subseries_ids</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>["S1005-A", "S1005-A-ext", "S1005-B", "S1005-B-ext", "S1005-C", "S1005-C-ext"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>subsource_ids</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>["FRED_AAA", "FRED_GS10", "SHILLER_ie_data", "USLR_ib10yr", "USLR_iblong", "USLR_ys"]</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/extenbooks/S1005_extenbook.xlsx
+++ b/extenbooks/S1005_extenbook.xlsx
@@ -15778,7 +15778,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A112"/>
+  <dimension ref="A1:A122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15868,7 +15868,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>**S1005** plots three rates on Figure 10.5:</t>
+          <t>**S1005** plots three rates on Figure 10.9:</t>
         </is>
       </c>
     </row>
@@ -16095,7 +16095,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>- Book: Shaikh (2016) Ch. 10 Fig 10.5, p. 466</t>
+          <t>- Book: Shaikh (2016) Ch. 10 Fig 10.9, Appendix 10.1</t>
         </is>
       </c>
     </row>
@@ -16394,6 +16394,68 @@
       <c r="A112" t="inlineStr">
         <is>
           <t>Informational only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>## Notation (plain-language key)</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>- **CD2 / CD3** — the predecessor builds of this dataset (earlier reconstructions; a "CD2 divergence" note reports how the earlier build differed, for information only).</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>- **Phase 5 / Phase 6** — Anu pipeline stages: Phase 5 is ingestion (building the book-period series); Phase 6 is extension (carrying the series forward with live data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>- **IROP / ROP** — incremental / average rate of profit (the return on newly added capital, or on the whole capital stock).</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>- **FRED** — the Federal Reserve Bank of St. Louis public economic-data service (source of the modern extension inputs).</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>- **BEA / NIPA** — the U.S. Bureau of Economic Analysis and its National Income and Product Accounts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>- **No-Lazy-Splices rule** — an internal quality rule: a derived (formula) quantity is never extended by splicing onto the published rate; the formula is recomputed from extended components so it stays analytically consistent across the book/extension boundary.</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>- **L01 / V03** — the load and validate scripts that build and check the series.</t>
         </is>
       </c>
     </row>
@@ -16905,7 +16967,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-05-18T22:26:09.120628+00:00</t>
+          <t>2026-07-02T11:16:37.210841+00:00</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S1005_extenbook.xlsx
+++ b/extenbooks/S1005_extenbook.xlsx
@@ -15831,7 +15831,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>**Status**: book_period_validated</t>
+          <t>**Status**: validated_book_and_extension</t>
         </is>
       </c>
     </row>
@@ -16967,7 +16967,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-02T11:16:37.210841+00:00</t>
+          <t>2026-07-11T03:44:22.227507+00:00</t>
         </is>
       </c>
     </row>
@@ -16982,11 +16982,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -17009,6 +17009,150 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>primary_source</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>USLR_ys</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>composite</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>validated_book_and_extension</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>validation_class</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>pipeline_consistent</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>triage</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>{"verdict": "publish", "reason": "Reconstructs Figure 10.9 (dividend yield vs bond yields) from Shiller and composite bond data; no proxies. Fixed figure reference (was 10.5, correct is 10.9).", "date": "2026-06-11"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>dpr</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/S1005_DPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>epr</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/S1005_EPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>content_type</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>time_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>proxy</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>publish</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>chapter</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
